--- a/RestaurantsSetup/ghazal-alreem-village/Book2.xlsx
+++ b/RestaurantsSetup/ghazal-alreem-village/Book2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedborsaly/restaurant-menu/RestaurantsSetup/ghazal-alreem-village/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E6EEF5-056D-CB49-8546-5B89A9511C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20DEAA2-05DB-9F41-84BB-4D2FCFC075D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{89EAB2C6-E3D1-1149-AF48-CB87DAEB172B}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="27240" windowHeight="16180" xr2:uid="{89EAB2C6-E3D1-1149-AF48-CB87DAEB172B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>Zane Expense</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>Sholder relocation operation</t>
+  </si>
+  <si>
+    <t>Emergency</t>
+  </si>
+  <si>
+    <t>Operation</t>
   </si>
 </sst>
 </file>
@@ -223,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -234,9 +240,8 @@
     <xf numFmtId="15" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -597,19 +602,19 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -626,7 +631,9 @@
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
@@ -641,7 +648,9 @@
       <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7">
@@ -656,27 +665,28 @@
       <c r="E5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="17">
         <f>SUM(C3:C5)</f>
         <v>1154.5550000000001</v>
       </c>
-      <c r="D6" s="19">
-        <v>30000</v>
-      </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="20"/>
+      <c r="D6" s="18">
+        <f>SUM(D3:D5)</f>
+        <v>39728.589999999997</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="11"/>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
@@ -765,31 +775,34 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12">
         <v>39.380000000000003</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <v>1336.58</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f>SUM(C8:C13)</f>
         <v>161.23000000000002</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
+      <c r="D14" s="14">
+        <f>SUM(D8:D13)</f>
+        <v>5561.58</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
